--- a/backend/data/attachments/wealth_家族信托设立咨询_2.xlsx
+++ b/backend/data/attachments/wealth_家族信托设立咨询_2.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="D2" t="n">
-        <v>7159</v>
+        <v>6180</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>283</v>
+        <v>479</v>
       </c>
       <c r="C3" t="n">
-        <v>221</v>
+        <v>121</v>
       </c>
       <c r="D3" t="n">
-        <v>3411</v>
+        <v>2786</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>532</v>
+        <v>1441</v>
       </c>
       <c r="C4" t="n">
-        <v>378</v>
+        <v>279</v>
       </c>
       <c r="D4" t="n">
-        <v>571</v>
+        <v>620</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>164</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>631</v>
+        <v>787</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -564,14 +564,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
